--- a/data/review/gpt-5.4-pro/step-2-review-reviewed.xlsx
+++ b/data/review/gpt-5.4-pro/step-2-review-reviewed.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="805">
   <si>
     <t>id</t>
   </si>
@@ -2601,18 +2601,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F409" displayName="step2" name="step2" id="1">
-  <autoFilter ref="$A$1:$F$409">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Include"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Exclude"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$F$409"/>
   <tableColumns count="6">
     <tableColumn name="id" id="1"/>
     <tableColumn name="title" id="2"/>
@@ -2855,7 +2844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="22.5" hidden="1" customHeight="1">
+    <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -2873,7 +2862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2891,7 +2880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -2909,7 +2898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
+    <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -2927,7 +2916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
+    <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -2945,7 +2934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
+    <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -2963,7 +2952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
+    <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -2981,7 +2970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
@@ -2999,7 +2988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
@@ -3017,7 +3006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
+    <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -3035,7 +3024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -3053,7 +3042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -3071,7 +3060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
+    <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -3089,7 +3078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
+    <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
@@ -3107,7 +3096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
+    <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>35</v>
       </c>
@@ -3125,7 +3114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
+    <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
@@ -3143,7 +3132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
+    <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
@@ -3161,7 +3150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
+    <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
@@ -3179,7 +3168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
+    <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
@@ -3197,7 +3186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" ht="15.75" hidden="1" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
@@ -3215,7 +3204,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="15.75" hidden="1" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>48</v>
       </c>
@@ -3233,7 +3222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
@@ -3251,7 +3240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" ht="15.75" hidden="1" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>52</v>
       </c>
@@ -3269,7 +3258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" ht="15.75" hidden="1" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>54</v>
       </c>
@@ -3287,7 +3276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" ht="15.75" hidden="1" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>56</v>
       </c>
@@ -3305,7 +3294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" ht="15.75" hidden="1" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>58</v>
       </c>
@@ -3323,7 +3312,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>60</v>
       </c>
@@ -3341,7 +3330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" ht="15.75" hidden="1" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>62</v>
       </c>
@@ -3359,7 +3348,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" ht="15.75" hidden="1" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>64</v>
       </c>
@@ -3379,7 +3368,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" ht="15.75" hidden="1" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>66</v>
       </c>
@@ -3397,7 +3386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" ht="15.75" hidden="1" customHeight="1">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>68</v>
       </c>
@@ -3415,7 +3404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" ht="15.75" hidden="1" customHeight="1">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>70</v>
       </c>
@@ -3433,7 +3422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" ht="15.75" hidden="1" customHeight="1">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>72</v>
       </c>
@@ -3451,7 +3440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" ht="15.75" hidden="1" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>74</v>
       </c>
@@ -3464,14 +3453,12 @@
       <c r="D35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" ht="15.75" hidden="1" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>76</v>
       </c>
@@ -3489,7 +3476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>78</v>
       </c>
@@ -3507,7 +3494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" ht="15.75" hidden="1" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>80</v>
       </c>
@@ -3525,7 +3512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" ht="15.75" hidden="1" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>82</v>
       </c>
@@ -3543,7 +3530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" ht="15.75" hidden="1" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>84</v>
       </c>
@@ -3561,7 +3548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" ht="15.75" hidden="1" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>86</v>
       </c>
@@ -3579,7 +3566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>88</v>
       </c>
@@ -3592,14 +3579,12 @@
       <c r="D42" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>90</v>
       </c>
@@ -3617,7 +3602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" ht="15.75" hidden="1" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>92</v>
       </c>
@@ -3635,7 +3620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>94</v>
       </c>
@@ -3653,7 +3638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" ht="15.75" hidden="1" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>96</v>
       </c>
@@ -3671,7 +3656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" ht="15.75" hidden="1" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>98</v>
       </c>
@@ -3689,7 +3674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" ht="15.75" hidden="1" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>100</v>
       </c>
@@ -3707,7 +3692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" ht="15.75" hidden="1" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>102</v>
       </c>
@@ -3725,7 +3710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" ht="15.75" hidden="1" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>104</v>
       </c>
@@ -3743,7 +3728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" ht="15.75" hidden="1" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>106</v>
       </c>
@@ -3761,7 +3746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" ht="15.75" hidden="1" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>108</v>
       </c>
@@ -3779,7 +3764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
         <v>110</v>
       </c>
@@ -3797,7 +3782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" ht="15.75" hidden="1" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>112</v>
       </c>
@@ -3815,7 +3800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" ht="15.75" hidden="1" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>114</v>
       </c>
@@ -3833,7 +3818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" ht="15.75" hidden="1" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>116</v>
       </c>
@@ -3851,7 +3836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" ht="15.75" hidden="1" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" ht="15.75" hidden="1" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
         <v>120</v>
       </c>
@@ -3887,7 +3872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" ht="15.75" hidden="1" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
         <v>122</v>
       </c>
@@ -3905,7 +3890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" ht="15.75" hidden="1" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
         <v>124</v>
       </c>
@@ -3923,7 +3908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" ht="15.75" hidden="1" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>126</v>
       </c>
@@ -3941,7 +3926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" ht="15.75" hidden="1" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
         <v>128</v>
       </c>
@@ -3959,7 +3944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" ht="15.75" hidden="1" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
         <v>130</v>
       </c>
@@ -3977,7 +3962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" ht="15.75" hidden="1" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
         <v>132</v>
       </c>
@@ -3995,7 +3980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" ht="15.75" hidden="1" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
         <v>134</v>
       </c>
@@ -4013,7 +3998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" ht="15.75" hidden="1" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
         <v>136</v>
       </c>
@@ -4031,7 +4016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" ht="15.75" hidden="1" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
         <v>138</v>
       </c>
@@ -4049,7 +4034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" ht="15.75" hidden="1" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
         <v>140</v>
       </c>
@@ -4067,7 +4052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" ht="15.75" hidden="1" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
         <v>142</v>
       </c>
@@ -4085,7 +4070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" ht="15.75" hidden="1" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
         <v>144</v>
       </c>
@@ -4103,7 +4088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" ht="15.75" hidden="1" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
         <v>146</v>
       </c>
@@ -4121,7 +4106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" ht="15.75" hidden="1" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
         <v>148</v>
       </c>
@@ -4139,7 +4124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" ht="15.75" hidden="1" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3" t="s">
         <v>150</v>
       </c>
@@ -4157,7 +4142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" ht="15.75" hidden="1" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
         <v>152</v>
       </c>
@@ -4175,7 +4160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" ht="15.75" hidden="1" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3" t="s">
         <v>154</v>
       </c>
@@ -4193,7 +4178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" ht="15.75" hidden="1" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
         <v>156</v>
       </c>
@@ -4211,7 +4196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" ht="15.75" hidden="1" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>158</v>
       </c>
@@ -4229,7 +4214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" ht="15.75" hidden="1" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
         <v>160</v>
       </c>
@@ -4247,7 +4232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" ht="15.75" hidden="1" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
         <v>162</v>
       </c>
@@ -4265,7 +4250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" ht="15.75" hidden="1" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
         <v>164</v>
       </c>
@@ -4283,7 +4268,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" ht="15.75" hidden="1" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
         <v>166</v>
       </c>
@@ -4301,7 +4286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" ht="15.75" hidden="1" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3" t="s">
         <v>168</v>
       </c>
@@ -4319,7 +4304,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" ht="15.75" hidden="1" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3" t="s">
         <v>170</v>
       </c>
@@ -4337,7 +4322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" ht="15.75" hidden="1" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>172</v>
       </c>
@@ -4355,7 +4340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" ht="15.75" hidden="1" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
         <v>174</v>
       </c>
@@ -4373,7 +4358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" ht="15.75" hidden="1" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>176</v>
       </c>
@@ -4391,7 +4376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" ht="15.75" hidden="1" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
         <v>178</v>
       </c>
@@ -4409,7 +4394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" ht="15.75" hidden="1" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3" t="s">
         <v>180</v>
       </c>
@@ -4427,7 +4412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" ht="15.75" hidden="1" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3" t="s">
         <v>182</v>
       </c>
@@ -4445,7 +4430,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" ht="15.75" hidden="1" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3" t="s">
         <v>184</v>
       </c>
@@ -4463,7 +4448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" ht="15.75" hidden="1" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3" t="s">
         <v>186</v>
       </c>
@@ -4481,7 +4466,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" ht="15.75" hidden="1" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3" t="s">
         <v>188</v>
       </c>
@@ -4499,7 +4484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" ht="15.75" hidden="1" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>190</v>
       </c>
@@ -4517,7 +4502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" ht="15.75" hidden="1" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3" t="s">
         <v>192</v>
       </c>
@@ -4535,7 +4520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" ht="15.75" hidden="1" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3" t="s">
         <v>194</v>
       </c>
@@ -4553,7 +4538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" ht="15.75" hidden="1" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3" t="s">
         <v>196</v>
       </c>
@@ -4571,7 +4556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" ht="15.75" hidden="1" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3" t="s">
         <v>198</v>
       </c>
@@ -4589,7 +4574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" ht="15.75" hidden="1" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3" t="s">
         <v>200</v>
       </c>
@@ -4607,7 +4592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" ht="15.75" hidden="1" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3" t="s">
         <v>202</v>
       </c>
@@ -4625,7 +4610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" ht="15.75" hidden="1" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3" t="s">
         <v>204</v>
       </c>
@@ -4643,7 +4628,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" ht="15.75" hidden="1" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3" t="s">
         <v>206</v>
       </c>
@@ -4661,7 +4646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" ht="15.75" hidden="1" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3" t="s">
         <v>208</v>
       </c>
@@ -4679,7 +4664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" ht="15.75" hidden="1" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3" t="s">
         <v>210</v>
       </c>
@@ -4697,7 +4682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" ht="15.75" hidden="1" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3" t="s">
         <v>212</v>
       </c>
@@ -4715,7 +4700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" ht="15.75" hidden="1" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3" t="s">
         <v>214</v>
       </c>
@@ -4733,7 +4718,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="106" ht="15.75" hidden="1" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3" t="s">
         <v>216</v>
       </c>
@@ -4751,7 +4736,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="107" ht="15.75" hidden="1" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3" t="s">
         <v>218</v>
       </c>
@@ -4769,7 +4754,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" ht="15.75" hidden="1" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3" t="s">
         <v>220</v>
       </c>
@@ -4787,7 +4772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" ht="15.75" hidden="1" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3" t="s">
         <v>222</v>
       </c>
@@ -4805,7 +4790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" ht="15.75" hidden="1" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3" t="s">
         <v>224</v>
       </c>
@@ -4823,7 +4808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" ht="15.75" hidden="1" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3" t="s">
         <v>226</v>
       </c>
@@ -4841,7 +4826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" ht="15.75" hidden="1" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3" t="s">
         <v>228</v>
       </c>
@@ -4859,7 +4844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" ht="15.75" hidden="1" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3" t="s">
         <v>230</v>
       </c>
@@ -4877,7 +4862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" ht="15.75" hidden="1" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3" t="s">
         <v>232</v>
       </c>
@@ -4895,7 +4880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" ht="15.75" hidden="1" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3" t="s">
         <v>234</v>
       </c>
@@ -4913,7 +4898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" ht="15.75" hidden="1" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3" t="s">
         <v>236</v>
       </c>
@@ -4931,7 +4916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" ht="15.75" hidden="1" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3" t="s">
         <v>238</v>
       </c>
@@ -4949,7 +4934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" ht="15.75" hidden="1" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3" t="s">
         <v>240</v>
       </c>
@@ -4967,7 +4952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" ht="15.75" hidden="1" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3" t="s">
         <v>242</v>
       </c>
@@ -4985,7 +4970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" ht="15.75" hidden="1" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3" t="s">
         <v>244</v>
       </c>
@@ -5003,7 +4988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" ht="15.75" hidden="1" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3" t="s">
         <v>246</v>
       </c>
@@ -5021,7 +5006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" ht="15.75" hidden="1" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3" t="s">
         <v>248</v>
       </c>
@@ -5039,7 +5024,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" ht="15.75" hidden="1" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3" t="s">
         <v>250</v>
       </c>
@@ -5057,7 +5042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" ht="15.75" hidden="1" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3" t="s">
         <v>252</v>
       </c>
@@ -5075,7 +5060,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="125" ht="15.75" hidden="1" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3" t="s">
         <v>254</v>
       </c>
@@ -5093,7 +5078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" ht="15.75" hidden="1" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3" t="s">
         <v>256</v>
       </c>
@@ -5111,7 +5096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" ht="15.75" hidden="1" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3" t="s">
         <v>258</v>
       </c>
@@ -5129,7 +5114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" ht="15.75" hidden="1" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3" t="s">
         <v>260</v>
       </c>
@@ -5147,7 +5132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" ht="15.75" hidden="1" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3" t="s">
         <v>262</v>
       </c>
@@ -5165,7 +5150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" ht="15.75" hidden="1" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" ht="15.75" hidden="1" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3" t="s">
         <v>266</v>
       </c>
@@ -5201,7 +5186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" ht="15.75" hidden="1" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3" t="s">
         <v>268</v>
       </c>
@@ -5219,7 +5204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" ht="15.75" hidden="1" customHeight="1">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3" t="s">
         <v>270</v>
       </c>
@@ -5237,7 +5222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" ht="15.75" hidden="1" customHeight="1">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3" t="s">
         <v>272</v>
       </c>
@@ -5255,7 +5240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" ht="15.75" hidden="1" customHeight="1">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3" t="s">
         <v>273</v>
       </c>
@@ -5273,7 +5258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" ht="15.75" hidden="1" customHeight="1">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3" t="s">
         <v>275</v>
       </c>
@@ -5291,7 +5276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" ht="15.75" hidden="1" customHeight="1">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>277</v>
       </c>
@@ -5309,7 +5294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" ht="15.75" hidden="1" customHeight="1">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3" t="s">
         <v>279</v>
       </c>
@@ -5347,7 +5332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" ht="15.75" hidden="1" customHeight="1">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3" t="s">
         <v>283</v>
       </c>
@@ -5365,7 +5350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" ht="15.75" hidden="1" customHeight="1">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3" t="s">
         <v>285</v>
       </c>
@@ -5383,7 +5368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" ht="15.75" hidden="1" customHeight="1">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3" t="s">
         <v>287</v>
       </c>
@@ -5401,7 +5386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" ht="15.75" hidden="1" customHeight="1">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3" t="s">
         <v>289</v>
       </c>
@@ -5419,7 +5404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" ht="15.75" hidden="1" customHeight="1">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="3" t="s">
         <v>291</v>
       </c>
@@ -5437,7 +5422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" ht="15.75" hidden="1" customHeight="1">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3" t="s">
         <v>293</v>
       </c>
@@ -5455,7 +5440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" ht="15.75" hidden="1" customHeight="1">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="3" t="s">
         <v>295</v>
       </c>
@@ -5473,7 +5458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" ht="15.75" hidden="1" customHeight="1">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3" t="s">
         <v>297</v>
       </c>
@@ -5491,7 +5476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" ht="15.75" hidden="1" customHeight="1">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="3" t="s">
         <v>299</v>
       </c>
@@ -5509,7 +5494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" ht="15.75" hidden="1" customHeight="1">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3" t="s">
         <v>301</v>
       </c>
@@ -5527,7 +5512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" ht="15.75" hidden="1" customHeight="1">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="3" t="s">
         <v>303</v>
       </c>
@@ -5545,7 +5530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" ht="15.75" hidden="1" customHeight="1">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3" t="s">
         <v>305</v>
       </c>
@@ -5563,7 +5548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" ht="15.75" hidden="1" customHeight="1">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="3" t="s">
         <v>306</v>
       </c>
@@ -5581,7 +5566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" ht="15.75" hidden="1" customHeight="1">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3" t="s">
         <v>308</v>
       </c>
@@ -5599,7 +5584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" ht="15.75" hidden="1" customHeight="1">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="3" t="s">
         <v>310</v>
       </c>
@@ -5617,7 +5602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" ht="15.75" hidden="1" customHeight="1">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="3" t="s">
         <v>312</v>
       </c>
@@ -5635,7 +5620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" ht="15.75" hidden="1" customHeight="1">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="3" t="s">
         <v>314</v>
       </c>
@@ -5653,7 +5638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" ht="15.75" hidden="1" customHeight="1">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="3" t="s">
         <v>316</v>
       </c>
@@ -5671,7 +5656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" ht="15.75" hidden="1" customHeight="1">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="3" t="s">
         <v>318</v>
       </c>
@@ -5689,7 +5674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" ht="15.75" hidden="1" customHeight="1">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="3" t="s">
         <v>320</v>
       </c>
@@ -5707,7 +5692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" ht="15.75" hidden="1" customHeight="1">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="3" t="s">
         <v>322</v>
       </c>
@@ -5725,7 +5710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" ht="15.75" hidden="1" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="3" t="s">
         <v>324</v>
       </c>
@@ -5743,7 +5728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" ht="15.75" hidden="1" customHeight="1">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="3" t="s">
         <v>326</v>
       </c>
@@ -5761,7 +5746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" ht="15.75" hidden="1" customHeight="1">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="3" t="s">
         <v>328</v>
       </c>
@@ -5779,7 +5764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" ht="15.75" hidden="1" customHeight="1">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="3" t="s">
         <v>330</v>
       </c>
@@ -5797,7 +5782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" ht="15.75" hidden="1" customHeight="1">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="3" t="s">
         <v>332</v>
       </c>
@@ -5815,7 +5800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" ht="15.75" hidden="1" customHeight="1">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="3" t="s">
         <v>334</v>
       </c>
@@ -5833,7 +5818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" ht="15.75" hidden="1" customHeight="1">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="3" t="s">
         <v>336</v>
       </c>
@@ -5851,7 +5836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" ht="15.75" hidden="1" customHeight="1">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="3" t="s">
         <v>338</v>
       </c>
@@ -5869,7 +5854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" ht="15.75" hidden="1" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="3" t="s">
         <v>340</v>
       </c>
@@ -5887,7 +5872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" ht="15.75" hidden="1" customHeight="1">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="3" t="s">
         <v>342</v>
       </c>
@@ -5905,7 +5890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" ht="15.75" hidden="1" customHeight="1">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="3" t="s">
         <v>344</v>
       </c>
@@ -5923,7 +5908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" ht="15.75" hidden="1" customHeight="1">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="3" t="s">
         <v>346</v>
       </c>
@@ -5941,7 +5926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" ht="15.75" hidden="1" customHeight="1">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="3" t="s">
         <v>348</v>
       </c>
@@ -5959,7 +5944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" ht="15.75" hidden="1" customHeight="1">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="3" t="s">
         <v>350</v>
       </c>
@@ -5977,7 +5962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" ht="15.75" hidden="1" customHeight="1">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="3" t="s">
         <v>352</v>
       </c>
@@ -5995,7 +5980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" ht="15.75" hidden="1" customHeight="1">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="3" t="s">
         <v>354</v>
       </c>
@@ -6013,7 +5998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" ht="15.75" hidden="1" customHeight="1">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="3" t="s">
         <v>356</v>
       </c>
@@ -6031,7 +6016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" ht="15.75" hidden="1" customHeight="1">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="3" t="s">
         <v>358</v>
       </c>
@@ -6049,7 +6034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" ht="15.75" hidden="1" customHeight="1">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="3" t="s">
         <v>360</v>
       </c>
@@ -6067,7 +6052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" ht="15.75" hidden="1" customHeight="1">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="3" t="s">
         <v>362</v>
       </c>
@@ -6085,7 +6070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" ht="15.75" hidden="1" customHeight="1">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="3" t="s">
         <v>364</v>
       </c>
@@ -6103,7 +6088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" ht="15.75" hidden="1" customHeight="1">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3" t="s">
         <v>366</v>
       </c>
@@ -6121,7 +6106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" ht="15.75" hidden="1" customHeight="1">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3" t="s">
         <v>368</v>
       </c>
@@ -6139,7 +6124,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="184" ht="15.75" hidden="1" customHeight="1">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3" t="s">
         <v>370</v>
       </c>
@@ -6157,7 +6142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" ht="15.75" hidden="1" customHeight="1">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="3" t="s">
         <v>372</v>
       </c>
@@ -6175,7 +6160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" ht="15.75" hidden="1" customHeight="1">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="3" t="s">
         <v>374</v>
       </c>
@@ -6193,7 +6178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" ht="15.75" hidden="1" customHeight="1">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="3" t="s">
         <v>376</v>
       </c>
@@ -6211,7 +6196,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="188" ht="15.75" hidden="1" customHeight="1">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="3" t="s">
         <v>378</v>
       </c>
@@ -6229,7 +6214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="189" ht="15.75" hidden="1" customHeight="1">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="3" t="s">
         <v>380</v>
       </c>
@@ -6247,7 +6232,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="190" ht="15.75" hidden="1" customHeight="1">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="3" t="s">
         <v>382</v>
       </c>
@@ -6265,7 +6250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" ht="15.75" hidden="1" customHeight="1">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="3" t="s">
         <v>384</v>
       </c>
@@ -6285,7 +6270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="192" ht="15.75" hidden="1" customHeight="1">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="3" t="s">
         <v>386</v>
       </c>
@@ -6303,7 +6288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" ht="15.75" hidden="1" customHeight="1">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="3" t="s">
         <v>388</v>
       </c>
@@ -6321,7 +6306,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="194" ht="15.75" hidden="1" customHeight="1">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="3" t="s">
         <v>390</v>
       </c>
@@ -6339,7 +6324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" ht="15.75" hidden="1" customHeight="1">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="3" t="s">
         <v>392</v>
       </c>
@@ -6357,7 +6342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" ht="15.75" hidden="1" customHeight="1">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="3" t="s">
         <v>394</v>
       </c>
@@ -6375,7 +6360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" ht="15.75" hidden="1" customHeight="1">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="3" t="s">
         <v>396</v>
       </c>
@@ -6393,7 +6378,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="198" ht="15.75" hidden="1" customHeight="1">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="3" t="s">
         <v>398</v>
       </c>
@@ -6411,7 +6396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="199" ht="15.75" hidden="1" customHeight="1">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="3" t="s">
         <v>400</v>
       </c>
@@ -6429,7 +6414,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="200" ht="15.75" hidden="1" customHeight="1">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="3" t="s">
         <v>402</v>
       </c>
@@ -6447,7 +6432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" ht="15.75" hidden="1" customHeight="1">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="3" t="s">
         <v>404</v>
       </c>
@@ -6465,7 +6450,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" ht="15.75" hidden="1" customHeight="1">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="3" t="s">
         <v>406</v>
       </c>
@@ -6485,7 +6470,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="203" ht="15.75" hidden="1" customHeight="1">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="3" t="s">
         <v>408</v>
       </c>
@@ -6503,7 +6488,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="204" ht="15.75" hidden="1" customHeight="1">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="3" t="s">
         <v>410</v>
       </c>
@@ -6521,7 +6506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" ht="15.75" hidden="1" customHeight="1">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="3" t="s">
         <v>412</v>
       </c>
@@ -6539,7 +6524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="206" ht="15.75" hidden="1" customHeight="1">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="3" t="s">
         <v>414</v>
       </c>
@@ -6557,7 +6542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" ht="15.75" hidden="1" customHeight="1">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="3" t="s">
         <v>416</v>
       </c>
@@ -6575,7 +6560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" ht="15.75" hidden="1" customHeight="1">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="3" t="s">
         <v>418</v>
       </c>
@@ -6593,7 +6578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" ht="15.75" hidden="1" customHeight="1">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="3" t="s">
         <v>420</v>
       </c>
@@ -6611,7 +6596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" ht="15.75" hidden="1" customHeight="1">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="3" t="s">
         <v>422</v>
       </c>
@@ -6629,7 +6614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" ht="15.75" hidden="1" customHeight="1">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="3" t="s">
         <v>424</v>
       </c>
@@ -6647,7 +6632,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="212" ht="15.75" hidden="1" customHeight="1">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="3" t="s">
         <v>426</v>
       </c>
@@ -6665,7 +6650,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="213" ht="15.75" hidden="1" customHeight="1">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="3" t="s">
         <v>428</v>
       </c>
@@ -6683,7 +6668,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="214" ht="15.75" hidden="1" customHeight="1">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="3" t="s">
         <v>430</v>
       </c>
@@ -6701,7 +6686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" ht="15.75" hidden="1" customHeight="1">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="3" t="s">
         <v>432</v>
       </c>
@@ -6719,7 +6704,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="216" ht="15.75" hidden="1" customHeight="1">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="3" t="s">
         <v>434</v>
       </c>
@@ -6737,7 +6722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" ht="15.75" hidden="1" customHeight="1">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="3" t="s">
         <v>436</v>
       </c>
@@ -6755,7 +6740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" ht="15.75" hidden="1" customHeight="1">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="3" t="s">
         <v>438</v>
       </c>
@@ -6775,7 +6760,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="219" ht="15.75" hidden="1" customHeight="1">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="3" t="s">
         <v>440</v>
       </c>
@@ -6793,7 +6778,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="220" ht="15.75" hidden="1" customHeight="1">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="3" t="s">
         <v>442</v>
       </c>
@@ -6811,7 +6796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="221" ht="15.75" hidden="1" customHeight="1">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="3" t="s">
         <v>444</v>
       </c>
@@ -6829,7 +6814,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="222" ht="15.75" hidden="1" customHeight="1">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="3" t="s">
         <v>446</v>
       </c>
@@ -6847,7 +6832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="223" ht="15.75" hidden="1" customHeight="1">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="3" t="s">
         <v>448</v>
       </c>
@@ -6865,7 +6850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="224" ht="15.75" hidden="1" customHeight="1">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="3" t="s">
         <v>450</v>
       </c>
@@ -6885,7 +6870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" ht="15.75" hidden="1" customHeight="1">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="3" t="s">
         <v>452</v>
       </c>
@@ -6903,7 +6888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" ht="15.75" hidden="1" customHeight="1">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="3" t="s">
         <v>454</v>
       </c>
@@ -6921,7 +6906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" ht="15.75" hidden="1" customHeight="1">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="3" t="s">
         <v>456</v>
       </c>
@@ -6939,7 +6924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" ht="15.75" hidden="1" customHeight="1">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="3" t="s">
         <v>458</v>
       </c>
@@ -6959,7 +6944,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="229" ht="15.75" hidden="1" customHeight="1">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="3" t="s">
         <v>460</v>
       </c>
@@ -6979,7 +6964,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="230" ht="15.75" hidden="1" customHeight="1">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="3" t="s">
         <v>462</v>
       </c>
@@ -6997,7 +6982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" ht="15.75" hidden="1" customHeight="1">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="3" t="s">
         <v>463</v>
       </c>
@@ -7015,7 +7000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" ht="15.75" hidden="1" customHeight="1">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="3" t="s">
         <v>465</v>
       </c>
@@ -7033,7 +7018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" ht="15.75" hidden="1" customHeight="1">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="3" t="s">
         <v>467</v>
       </c>
@@ -7051,7 +7036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="234" ht="15.75" hidden="1" customHeight="1">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="3" t="s">
         <v>469</v>
       </c>
@@ -7069,7 +7054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="235" ht="15.75" hidden="1" customHeight="1">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="3" t="s">
         <v>471</v>
       </c>
@@ -7087,7 +7072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="236" ht="15.75" hidden="1" customHeight="1">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="3" t="s">
         <v>473</v>
       </c>
@@ -7105,7 +7090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="237" ht="15.75" hidden="1" customHeight="1">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="3" t="s">
         <v>475</v>
       </c>
@@ -7123,7 +7108,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="238" ht="15.75" hidden="1" customHeight="1">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="3" t="s">
         <v>477</v>
       </c>
@@ -7143,7 +7128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="239" ht="15.75" hidden="1" customHeight="1">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="3" t="s">
         <v>479</v>
       </c>
@@ -7163,7 +7148,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" ht="15.75" hidden="1" customHeight="1">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="3" t="s">
         <v>481</v>
       </c>
@@ -7181,7 +7166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" ht="15.75" hidden="1" customHeight="1">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="3" t="s">
         <v>483</v>
       </c>
@@ -7199,7 +7184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="242" ht="15.75" hidden="1" customHeight="1">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="3" t="s">
         <v>485</v>
       </c>
@@ -7217,7 +7202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="243" ht="15.75" hidden="1" customHeight="1">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="3" t="s">
         <v>487</v>
       </c>
@@ -7237,7 +7222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="244" ht="15.75" hidden="1" customHeight="1">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="3" t="s">
         <v>489</v>
       </c>
@@ -7257,7 +7242,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="245" ht="15.75" hidden="1" customHeight="1">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="3" t="s">
         <v>491</v>
       </c>
@@ -7277,7 +7262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" ht="15.75" hidden="1" customHeight="1">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="3" t="s">
         <v>493</v>
       </c>
@@ -7295,7 +7280,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="247" ht="15.75" hidden="1" customHeight="1">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="3" t="s">
         <v>495</v>
       </c>
@@ -7315,7 +7300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" ht="15.75" hidden="1" customHeight="1">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="3" t="s">
         <v>497</v>
       </c>
@@ -7333,7 +7318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" ht="15.75" hidden="1" customHeight="1">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="3" t="s">
         <v>499</v>
       </c>
@@ -7351,7 +7336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" ht="15.75" hidden="1" customHeight="1">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="3" t="s">
         <v>501</v>
       </c>
@@ -7369,7 +7354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="251" ht="15.75" hidden="1" customHeight="1">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="3" t="s">
         <v>503</v>
       </c>
@@ -7387,7 +7372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" ht="15.75" hidden="1" customHeight="1">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="3" t="s">
         <v>505</v>
       </c>
@@ -7405,7 +7390,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="253" ht="15.75" hidden="1" customHeight="1">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="3" t="s">
         <v>507</v>
       </c>
@@ -7423,7 +7408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="254" ht="15.75" hidden="1" customHeight="1">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="3" t="s">
         <v>509</v>
       </c>
@@ -7441,7 +7426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="255" ht="15.75" hidden="1" customHeight="1">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="3" t="s">
         <v>511</v>
       </c>
@@ -7459,7 +7444,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="256" ht="15.75" hidden="1" customHeight="1">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="3" t="s">
         <v>513</v>
       </c>
@@ -7479,7 +7464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="257" ht="15.75" hidden="1" customHeight="1">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="3" t="s">
         <v>515</v>
       </c>
@@ -7497,7 +7482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="258" ht="15.75" hidden="1" customHeight="1">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="3" t="s">
         <v>517</v>
       </c>
@@ -7517,7 +7502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="259" ht="15.75" hidden="1" customHeight="1">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="3" t="s">
         <v>519</v>
       </c>
@@ -7535,7 +7520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="260" ht="15.75" hidden="1" customHeight="1">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="3" t="s">
         <v>521</v>
       </c>
@@ -7555,7 +7540,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="261" ht="15.75" hidden="1" customHeight="1">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="3" t="s">
         <v>523</v>
       </c>
@@ -7573,7 +7558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" ht="15.75" hidden="1" customHeight="1">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="3" t="s">
         <v>525</v>
       </c>
@@ -7593,7 +7578,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="263" ht="15.75" hidden="1" customHeight="1">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="3" t="s">
         <v>527</v>
       </c>
@@ -7611,7 +7596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="264" ht="15.75" hidden="1" customHeight="1">
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="3" t="s">
         <v>529</v>
       </c>
@@ -7629,7 +7614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="265" ht="15.75" hidden="1" customHeight="1">
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="3" t="s">
         <v>531</v>
       </c>
@@ -7647,7 +7632,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="266" ht="15.75" hidden="1" customHeight="1">
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="3" t="s">
         <v>533</v>
       </c>
@@ -7665,7 +7650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="267" ht="15.75" hidden="1" customHeight="1">
+    <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="3" t="s">
         <v>535</v>
       </c>
@@ -7683,7 +7668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="268" ht="15.75" hidden="1" customHeight="1">
+    <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="3" t="s">
         <v>537</v>
       </c>
@@ -7701,7 +7686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="269" ht="15.75" hidden="1" customHeight="1">
+    <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="3" t="s">
         <v>539</v>
       </c>
@@ -7719,7 +7704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="270" ht="15.75" hidden="1" customHeight="1">
+    <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="3" t="s">
         <v>541</v>
       </c>
@@ -7737,7 +7722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" ht="15.75" hidden="1" customHeight="1">
+    <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="3" t="s">
         <v>543</v>
       </c>
@@ -7755,7 +7740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" ht="15.75" hidden="1" customHeight="1">
+    <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="3" t="s">
         <v>545</v>
       </c>
@@ -7773,7 +7758,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="273" ht="15.75" hidden="1" customHeight="1">
+    <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="3" t="s">
         <v>547</v>
       </c>
@@ -7791,7 +7776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" ht="15.75" hidden="1" customHeight="1">
+    <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="3" t="s">
         <v>549</v>
       </c>
@@ -7809,7 +7794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" ht="15.75" hidden="1" customHeight="1">
+    <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="3" t="s">
         <v>551</v>
       </c>
@@ -7827,7 +7812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="276" ht="15.75" hidden="1" customHeight="1">
+    <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="3" t="s">
         <v>553</v>
       </c>
@@ -7845,7 +7830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="277" ht="15.75" hidden="1" customHeight="1">
+    <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="3" t="s">
         <v>555</v>
       </c>
@@ -7865,7 +7850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="278" ht="15.75" hidden="1" customHeight="1">
+    <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="3" t="s">
         <v>557</v>
       </c>
@@ -7883,7 +7868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" ht="15.75" hidden="1" customHeight="1">
+    <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="3" t="s">
         <v>559</v>
       </c>
@@ -7903,7 +7888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" ht="15.75" hidden="1" customHeight="1">
+    <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="3" t="s">
         <v>561</v>
       </c>
@@ -7916,14 +7901,12 @@
       <c r="D280" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E280" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="E280" s="7"/>
       <c r="F280" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="281" ht="15.75" hidden="1" customHeight="1">
+    <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="3" t="s">
         <v>563</v>
       </c>
@@ -7941,7 +7924,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="282" ht="15.75" hidden="1" customHeight="1">
+    <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="3" t="s">
         <v>565</v>
       </c>
@@ -7961,7 +7944,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="283" ht="15.75" hidden="1" customHeight="1">
+    <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="3" t="s">
         <v>567</v>
       </c>
@@ -7979,7 +7962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="284" ht="15.75" hidden="1" customHeight="1">
+    <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="3" t="s">
         <v>569</v>
       </c>
@@ -7997,7 +7980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="285" ht="15.75" hidden="1" customHeight="1">
+    <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="3" t="s">
         <v>571</v>
       </c>
@@ -8035,7 +8018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="287" ht="15.75" hidden="1" customHeight="1">
+    <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="3" t="s">
         <v>575</v>
       </c>
@@ -8053,7 +8036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="288" ht="15.75" hidden="1" customHeight="1">
+    <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="3" t="s">
         <v>577</v>
       </c>
@@ -8071,7 +8054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="289" ht="15.75" hidden="1" customHeight="1">
+    <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="3" t="s">
         <v>579</v>
       </c>
@@ -8089,7 +8072,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="290" ht="15.75" hidden="1" customHeight="1">
+    <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="3" t="s">
         <v>581</v>
       </c>
@@ -8127,7 +8110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="292" ht="15.75" hidden="1" customHeight="1">
+    <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="3" t="s">
         <v>585</v>
       </c>
@@ -8145,7 +8128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="293" ht="15.75" hidden="1" customHeight="1">
+    <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="3" t="s">
         <v>587</v>
       </c>
@@ -8165,7 +8148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="294" ht="15.75" hidden="1" customHeight="1">
+    <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="3" t="s">
         <v>589</v>
       </c>
@@ -8183,7 +8166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="295" ht="15.75" hidden="1" customHeight="1">
+    <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="3" t="s">
         <v>591</v>
       </c>
@@ -8201,7 +8184,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="296" ht="15.75" hidden="1" customHeight="1">
+    <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="3" t="s">
         <v>593</v>
       </c>
@@ -8219,7 +8202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" ht="15.75" hidden="1" customHeight="1">
+    <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="3" t="s">
         <v>595</v>
       </c>
@@ -8237,7 +8220,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="298" ht="15.75" hidden="1" customHeight="1">
+    <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="3" t="s">
         <v>597</v>
       </c>
@@ -8255,7 +8238,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="299" ht="15.75" hidden="1" customHeight="1">
+    <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="3" t="s">
         <v>599</v>
       </c>
@@ -8273,7 +8256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="300" ht="15.75" hidden="1" customHeight="1">
+    <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="3" t="s">
         <v>601</v>
       </c>
@@ -8291,7 +8274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="301" ht="15.75" hidden="1" customHeight="1">
+    <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="3" t="s">
         <v>603</v>
       </c>
@@ -8312,7 +8295,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="302" ht="15.75" hidden="1" customHeight="1">
+    <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="3" t="s">
         <v>606</v>
       </c>
@@ -8332,7 +8315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="303" ht="15.75" hidden="1" customHeight="1">
+    <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="3" t="s">
         <v>608</v>
       </c>
@@ -8350,7 +8333,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="304" ht="15.75" hidden="1" customHeight="1">
+    <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="3" t="s">
         <v>610</v>
       </c>
@@ -8368,7 +8351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="305" ht="15.75" hidden="1" customHeight="1">
+    <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="3" t="s">
         <v>612</v>
       </c>
@@ -8386,7 +8369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="306" ht="15.75" hidden="1" customHeight="1">
+    <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="3" t="s">
         <v>614</v>
       </c>
@@ -8404,7 +8387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" ht="15.75" hidden="1" customHeight="1">
+    <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="3" t="s">
         <v>616</v>
       </c>
@@ -8422,7 +8405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="308" ht="15.75" hidden="1" customHeight="1">
+    <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="3" t="s">
         <v>617</v>
       </c>
@@ -8440,7 +8423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" ht="15.75" hidden="1" customHeight="1">
+    <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="3" t="s">
         <v>619</v>
       </c>
@@ -8460,7 +8443,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="310" ht="15.75" hidden="1" customHeight="1">
+    <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="3" t="s">
         <v>621</v>
       </c>
@@ -8480,7 +8463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="311" ht="15.75" hidden="1" customHeight="1">
+    <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="3" t="s">
         <v>623</v>
       </c>
@@ -8498,7 +8481,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="312" ht="15.75" hidden="1" customHeight="1">
+    <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="3" t="s">
         <v>625</v>
       </c>
@@ -8516,7 +8499,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="313" ht="15.75" hidden="1" customHeight="1">
+    <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="3" t="s">
         <v>627</v>
       </c>
@@ -8534,7 +8517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" ht="15.75" hidden="1" customHeight="1">
+    <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="3" t="s">
         <v>629</v>
       </c>
@@ -8552,7 +8535,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="315" ht="15.75" hidden="1" customHeight="1">
+    <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="3" t="s">
         <v>631</v>
       </c>
@@ -8570,7 +8553,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="316" ht="15.75" hidden="1" customHeight="1">
+    <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="3" t="s">
         <v>633</v>
       </c>
@@ -8588,7 +8571,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="317" ht="15.75" hidden="1" customHeight="1">
+    <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="3" t="s">
         <v>635</v>
       </c>
@@ -8606,7 +8589,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="318" ht="15.75" hidden="1" customHeight="1">
+    <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="3" t="s">
         <v>637</v>
       </c>
@@ -8624,7 +8607,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="319" ht="15.75" hidden="1" customHeight="1">
+    <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="3" t="s">
         <v>639</v>
       </c>
@@ -8644,7 +8627,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="320" ht="15.75" hidden="1" customHeight="1">
+    <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="3" t="s">
         <v>641</v>
       </c>
@@ -8662,7 +8645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="321" ht="15.75" hidden="1" customHeight="1">
+    <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="3" t="s">
         <v>643</v>
       </c>
@@ -8680,7 +8663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="322" ht="15.75" hidden="1" customHeight="1">
+    <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="3" t="s">
         <v>645</v>
       </c>
@@ -8700,7 +8683,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="323" ht="15.75" hidden="1" customHeight="1">
+    <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="3" t="s">
         <v>647</v>
       </c>
@@ -8718,7 +8701,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="324" ht="15.75" hidden="1" customHeight="1">
+    <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="3" t="s">
         <v>649</v>
       </c>
@@ -8736,7 +8719,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="325" ht="15.75" hidden="1" customHeight="1">
+    <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="3" t="s">
         <v>651</v>
       </c>
@@ -8754,7 +8737,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="326" ht="15.75" hidden="1" customHeight="1">
+    <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="3" t="s">
         <v>653</v>
       </c>
@@ -8772,7 +8755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="327" ht="15.75" hidden="1" customHeight="1">
+    <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="3" t="s">
         <v>655</v>
       </c>
@@ -8790,7 +8773,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="328" ht="15.75" hidden="1" customHeight="1">
+    <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="3" t="s">
         <v>657</v>
       </c>
@@ -8808,7 +8791,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="329" ht="15.75" hidden="1" customHeight="1">
+    <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="3" t="s">
         <v>659</v>
       </c>
@@ -8826,7 +8809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="330" ht="15.75" hidden="1" customHeight="1">
+    <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="3" t="s">
         <v>661</v>
       </c>
@@ -8844,7 +8827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="331" ht="15.75" hidden="1" customHeight="1">
+    <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="3" t="s">
         <v>663</v>
       </c>
@@ -8862,7 +8845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="332" ht="15.75" hidden="1" customHeight="1">
+    <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="3" t="s">
         <v>665</v>
       </c>
@@ -8880,7 +8863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="333" ht="15.75" hidden="1" customHeight="1">
+    <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="3" t="s">
         <v>667</v>
       </c>
@@ -8898,7 +8881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="334" ht="15.75" hidden="1" customHeight="1">
+    <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="3" t="s">
         <v>669</v>
       </c>
@@ -8916,7 +8899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="335" ht="15.75" hidden="1" customHeight="1">
+    <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="3" t="s">
         <v>671</v>
       </c>
@@ -8934,7 +8917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="336" ht="15.75" hidden="1" customHeight="1">
+    <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="3" t="s">
         <v>673</v>
       </c>
@@ -8952,7 +8935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="337" ht="15.75" hidden="1" customHeight="1">
+    <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="3" t="s">
         <v>675</v>
       </c>
@@ -8970,7 +8953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="338" ht="15.75" hidden="1" customHeight="1">
+    <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="3" t="s">
         <v>677</v>
       </c>
@@ -8988,7 +8971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="339" ht="15.75" hidden="1" customHeight="1">
+    <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="3" t="s">
         <v>679</v>
       </c>
@@ -9006,7 +8989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" ht="15.75" hidden="1" customHeight="1">
+    <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="3" t="s">
         <v>681</v>
       </c>
@@ -9024,7 +9007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" ht="15.75" hidden="1" customHeight="1">
+    <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="3" t="s">
         <v>683</v>
       </c>
@@ -9042,7 +9025,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" ht="15.75" hidden="1" customHeight="1">
+    <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="3" t="s">
         <v>685</v>
       </c>
@@ -9060,7 +9043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="343" ht="15.75" hidden="1" customHeight="1">
+    <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="3" t="s">
         <v>687</v>
       </c>
@@ -9078,7 +9061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" ht="15.75" hidden="1" customHeight="1">
+    <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="3" t="s">
         <v>689</v>
       </c>
@@ -9096,7 +9079,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="345" ht="15.75" hidden="1" customHeight="1">
+    <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="3" t="s">
         <v>691</v>
       </c>
@@ -9114,7 +9097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="346" ht="15.75" hidden="1" customHeight="1">
+    <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="3" t="s">
         <v>693</v>
       </c>
@@ -9132,7 +9115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" ht="15.75" hidden="1" customHeight="1">
+    <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="3" t="s">
         <v>695</v>
       </c>
@@ -9150,7 +9133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="348" ht="15.75" hidden="1" customHeight="1">
+    <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="3" t="s">
         <v>697</v>
       </c>
@@ -9168,7 +9151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="349" ht="15.75" hidden="1" customHeight="1">
+    <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="3" t="s">
         <v>699</v>
       </c>
@@ -9186,7 +9169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="350" ht="15.75" hidden="1" customHeight="1">
+    <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="3" t="s">
         <v>701</v>
       </c>
@@ -9204,7 +9187,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="351" ht="15.75" hidden="1" customHeight="1">
+    <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="3" t="s">
         <v>703</v>
       </c>
@@ -9222,7 +9205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="352" ht="15.75" hidden="1" customHeight="1">
+    <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="3" t="s">
         <v>705</v>
       </c>
@@ -9240,7 +9223,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="353" ht="15.75" hidden="1" customHeight="1">
+    <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="3" t="s">
         <v>707</v>
       </c>
@@ -9258,7 +9241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="354" ht="15.75" hidden="1" customHeight="1">
+    <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="3" t="s">
         <v>709</v>
       </c>
@@ -9276,7 +9259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" ht="15.75" hidden="1" customHeight="1">
+    <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="3" t="s">
         <v>711</v>
       </c>
@@ -9294,7 +9277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="356" ht="15.75" hidden="1" customHeight="1">
+    <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="3" t="s">
         <v>713</v>
       </c>
@@ -9312,7 +9295,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" ht="15.75" hidden="1" customHeight="1">
+    <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="3" t="s">
         <v>715</v>
       </c>
@@ -9330,7 +9313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" ht="15.75" hidden="1" customHeight="1">
+    <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="3" t="s">
         <v>717</v>
       </c>
@@ -9348,7 +9331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="359" ht="15.75" hidden="1" customHeight="1">
+    <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="3" t="s">
         <v>719</v>
       </c>
@@ -9366,7 +9349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="360" ht="15.75" hidden="1" customHeight="1">
+    <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="3" t="s">
         <v>721</v>
       </c>
@@ -9384,7 +9367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="361" ht="15.75" hidden="1" customHeight="1">
+    <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="3" t="s">
         <v>723</v>
       </c>
@@ -9402,7 +9385,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="362" ht="15.75" hidden="1" customHeight="1">
+    <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="3" t="s">
         <v>725</v>
       </c>
@@ -9420,7 +9403,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="363" ht="15.75" hidden="1" customHeight="1">
+    <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="3" t="s">
         <v>727</v>
       </c>
@@ -9438,7 +9421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="364" ht="15.75" hidden="1" customHeight="1">
+    <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="3" t="s">
         <v>729</v>
       </c>
@@ -9456,7 +9439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="365" ht="15.75" hidden="1" customHeight="1">
+    <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="3" t="s">
         <v>731</v>
       </c>
@@ -9474,7 +9457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" ht="15.75" hidden="1" customHeight="1">
+    <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="3" t="s">
         <v>733</v>
       </c>
@@ -9492,7 +9475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="367" ht="15.75" hidden="1" customHeight="1">
+    <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="3" t="s">
         <v>735</v>
       </c>
@@ -9510,7 +9493,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="368" ht="15.75" hidden="1" customHeight="1">
+    <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="3" t="s">
         <v>737</v>
       </c>
@@ -9528,7 +9511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" ht="15.75" hidden="1" customHeight="1">
+    <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="3" t="s">
         <v>739</v>
       </c>
@@ -9546,7 +9529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="370" ht="15.75" hidden="1" customHeight="1">
+    <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="3" t="s">
         <v>741</v>
       </c>
@@ -9564,7 +9547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" ht="15.75" hidden="1" customHeight="1">
+    <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="3" t="s">
         <v>743</v>
       </c>
@@ -9582,7 +9565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" ht="15.75" hidden="1" customHeight="1">
+    <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="3" t="s">
         <v>745</v>
       </c>
@@ -9600,7 +9583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" ht="15.75" hidden="1" customHeight="1">
+    <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="3" t="s">
         <v>747</v>
       </c>
@@ -9618,7 +9601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" ht="15.75" hidden="1" customHeight="1">
+    <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="3" t="s">
         <v>749</v>
       </c>
@@ -9638,7 +9621,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="375" ht="15.75" hidden="1" customHeight="1">
+    <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="3" t="s">
         <v>751</v>
       </c>
@@ -9656,7 +9639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" ht="15.75" hidden="1" customHeight="1">
+    <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="3" t="s">
         <v>753</v>
       </c>
@@ -9674,7 +9657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="377" ht="15.75" hidden="1" customHeight="1">
+    <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="3" t="s">
         <v>754</v>
       </c>
@@ -9692,7 +9675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="378" ht="15.75" hidden="1" customHeight="1">
+    <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="3" t="s">
         <v>756</v>
       </c>
@@ -9710,7 +9693,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="379" ht="15.75" hidden="1" customHeight="1">
+    <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="3" t="s">
         <v>758</v>
       </c>
@@ -9728,7 +9711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="380" ht="15.75" hidden="1" customHeight="1">
+    <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="3" t="s">
         <v>760</v>
       </c>
@@ -9746,7 +9729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="381" ht="15.75" hidden="1" customHeight="1">
+    <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="3" t="s">
         <v>762</v>
       </c>
@@ -9764,7 +9747,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="382" ht="15.75" hidden="1" customHeight="1">
+    <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="3" t="s">
         <v>764</v>
       </c>
@@ -9782,7 +9765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="383" ht="15.75" hidden="1" customHeight="1">
+    <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="3" t="s">
         <v>766</v>
       </c>
@@ -9800,7 +9783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="384" ht="15.75" hidden="1" customHeight="1">
+    <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="3" t="s">
         <v>768</v>
       </c>
@@ -9818,7 +9801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="385" ht="15.75" hidden="1" customHeight="1">
+    <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="3" t="s">
         <v>770</v>
       </c>
@@ -9838,7 +9821,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="386" ht="15.75" hidden="1" customHeight="1">
+    <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="3" t="s">
         <v>772</v>
       </c>
@@ -9858,7 +9841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="387" ht="15.75" hidden="1" customHeight="1">
+    <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="3" t="s">
         <v>773</v>
       </c>
@@ -9876,7 +9859,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="388" ht="15.75" hidden="1" customHeight="1">
+    <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="3" t="s">
         <v>775</v>
       </c>
@@ -9894,7 +9877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="389" ht="15.75" hidden="1" customHeight="1">
+    <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="3" t="s">
         <v>776</v>
       </c>
@@ -9912,7 +9895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" ht="15.75" hidden="1" customHeight="1">
+    <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="3" t="s">
         <v>778</v>
       </c>
@@ -9932,7 +9915,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="391" ht="15.75" hidden="1" customHeight="1">
+    <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="3" t="s">
         <v>779</v>
       </c>
@@ -9952,7 +9935,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="392" ht="15.75" hidden="1" customHeight="1">
+    <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="3" t="s">
         <v>780</v>
       </c>
@@ -9972,7 +9955,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="393" ht="15.75" hidden="1" customHeight="1">
+    <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="3" t="s">
         <v>781</v>
       </c>
@@ -9992,7 +9975,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="394" ht="15.75" hidden="1" customHeight="1">
+    <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="3" t="s">
         <v>782</v>
       </c>
@@ -10012,7 +9995,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="395" ht="15.75" hidden="1" customHeight="1">
+    <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="3" t="s">
         <v>783</v>
       </c>
@@ -10032,7 +10015,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="396" ht="15.75" hidden="1" customHeight="1">
+    <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="3" t="s">
         <v>784</v>
       </c>
@@ -10052,7 +10035,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="397" ht="15.75" hidden="1" customHeight="1">
+    <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="3" t="s">
         <v>785</v>
       </c>
@@ -10092,7 +10075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="399" ht="15.75" hidden="1" customHeight="1">
+    <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="3" t="s">
         <v>788</v>
       </c>
@@ -10130,7 +10113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="401" ht="15.75" hidden="1" customHeight="1">
+    <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="3" t="s">
         <v>792</v>
       </c>
@@ -10150,7 +10133,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="402" ht="15.75" hidden="1" customHeight="1">
+    <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="3" t="s">
         <v>794</v>
       </c>
@@ -10170,7 +10153,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="403" ht="15.75" hidden="1" customHeight="1">
+    <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="3" t="s">
         <v>795</v>
       </c>
@@ -10188,7 +10171,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="404" ht="15.75" hidden="1" customHeight="1">
+    <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="3" t="s">
         <v>797</v>
       </c>
@@ -10206,7 +10189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="405" ht="15.75" hidden="1" customHeight="1">
+    <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="3" t="s">
         <v>799</v>
       </c>
@@ -10226,7 +10209,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="406" ht="15.75" hidden="1" customHeight="1">
+    <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="3" t="s">
         <v>800</v>
       </c>
@@ -10246,7 +10229,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="407" ht="15.75" hidden="1" customHeight="1">
+    <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="3" t="s">
         <v>801</v>
       </c>
@@ -10266,7 +10249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="408" ht="15.75" hidden="1" customHeight="1">
+    <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="3" t="s">
         <v>802</v>
       </c>
@@ -10286,7 +10269,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="409" ht="15.75" hidden="1" customHeight="1">
+    <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="3" t="s">
         <v>803</v>
       </c>
